--- a/data/sxbet/ligas/Ligue 1/trades.xlsx
+++ b/data/sxbet/ligas/Ligue 1/trades.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V3"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -531,102 +531,94 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0xc746abb44ed75d1109db0356b498f400bc4189fb19e3260c47b9d78714946cf3</t>
+          <t>0xafdf54be0646dba4510efcda2e124e07351eb3359e0c9f65e1c6e2eb14e6ada2</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0x7CA12ef070eAc708909d595aF0A62fb964e82eB8</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>29.98926</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>1.59</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Asian Handicap (-1)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Olympique Marseille vs Strasbourg</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Olympique Marseille</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0xb9fe47a3d72b08eea33d5e5f5f940f7fcbff49c92ebfecc270ccabb76447a0cc</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>L19386147</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>40.56999</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Asian Handicap (0.5)</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Toulouse +0.5</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Ligue 1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Toulouse vs Lyon</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Toulouse</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Lyon</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>0xefbf5a2bfb2ef6778266b71834e81eb0d82f5cb1a7911929005ad7ccdefcea50</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>L19386108</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>SUCCESS</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>1786871979</t>
+          <t>1786891933</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>1787424300</t>
+          <t>1787337900</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>67.61665</t>
+          <t>50.829254</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
@@ -643,23 +635,23 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0x585756fb6d6e2cd22ccc74ffdb29c637ae637187138cd0c92c104bb2c12c9cdc</t>
+          <t>0x6be3f22ac3e629082c71958d81e6f9de67b99250c6b90b1bbf34a8455113d3b3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+          <t>0x8268feC8dCb0D284343054BDf2b649286c9aA0a1</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>1.12076</t>
+          <t>44.56935</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.4575</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -720,25 +712,241 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>1786891932</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1787337900</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>97.419344</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>0xc746abb44ed75d1109db0356b498f400bc4189fb19e3260c47b9d78714946cf3</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0x7CA12ef070eAc708909d595aF0A62fb964e82eB8</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>40.56999</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asian Handicap (0.5)</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Toulouse +0.5</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Toulouse vs Lyon</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Toulouse</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Lyon</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0xefbf5a2bfb2ef6778266b71834e81eb0d82f5cb1a7911929005ad7ccdefcea50</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>L19386108</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>1786871979</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1787424300</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>67.61665</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>SXR</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>0x585756fb6d6e2cd22ccc74ffdb29c637ae637187138cd0c92c104bb2c12c9cdc</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>0x7E3a6e22cac4eECeceCc7D9086d7c0fE1195Ec16</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>1.12076</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1X2</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Ligue 1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Olympique Marseille vs Strasbourg</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Olympique Marseille</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Strasbourg</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0xd4a770ce11593e7632e8c47abe142daa78da006febb11e96fad7b956f68bae94</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>L19386147</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>SUCCESS</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
           <t>1786870742</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>1787337900</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>2.436435</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>SXR</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0x6629Ce1Cf35Cc1329ebB4F63202F3f197b3F050B</t>
         </is>
